--- a/三合一單自動產生器/台積電槽車barcode三合一單-範本.xlsx
+++ b/三合一單自動產生器/台積電槽車barcode三合一單-範本.xlsx
@@ -428,6 +428,35 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -435,24 +464,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -474,17 +485,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -515,7 +515,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2696625</xdr:colOff>
+      <xdr:colOff>1538385</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -1029,43 +1029,43 @@
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" customWidth="1"/>
     <col min="5" max="5" width="42.21875" customWidth="1"/>
     <col min="15" max="15" width="48.88671875" customWidth="1"/>
     <col min="17" max="17" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
     </row>
     <row r="2" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="15" t="s">
@@ -1079,9 +1079,9 @@
         <f>$D$3</f>
         <v>*4L12C53161*</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -1091,16 +1091,16 @@
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="14"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="16"/>
       <c r="D4" s="18"/>
       <c r="E4" s="4" t="str">
         <f>$C$3</f>
         <v>4L12C53161</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -1110,10 +1110,10 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="22" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="17" t="str">
@@ -1124,41 +1124,41 @@
         <f>$D$5</f>
         <v>*5E319*</v>
       </c>
-      <c r="F5" s="25"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
     </row>
     <row r="6" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="14"/>
-      <c r="C6" s="20"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="18"/>
       <c r="E6" s="8" t="str">
         <f>$C$5</f>
         <v>5E319</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
     </row>
     <row r="7" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="24" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="17" t="str">
@@ -1169,38 +1169,38 @@
         <f>$D$7</f>
         <v>*626206E3191*</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
     </row>
     <row r="8" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="14"/>
-      <c r="C8" s="22"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="18"/>
       <c r="E8" s="4" t="str">
         <f>$C$7</f>
         <v>626206E3191</v>
       </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
     </row>
     <row r="9" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="15">
@@ -1214,39 +1214,39 @@
         <f>$D$9</f>
         <v>*375970680*</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
     </row>
     <row r="10" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="14"/>
+      <c r="B10" s="11"/>
       <c r="C10" s="16"/>
       <c r="D10" s="18"/>
       <c r="E10" s="4">
         <f>$C$9</f>
         <v>375970680</v>
       </c>
-      <c r="F10" s="25"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
       <c r="Q10" s="6"/>
     </row>
     <row r="11" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="15" t="s">
@@ -1260,79 +1260,79 @@
         <f>$D$11</f>
         <v>*E1550156A*</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
     </row>
     <row r="12" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="14"/>
+      <c r="B12" s="11"/>
       <c r="C12" s="16"/>
       <c r="D12" s="18"/>
       <c r="E12" s="4" t="str">
         <f>$C$11</f>
         <v>E1550156A</v>
       </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
     </row>
     <row r="13" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
     </row>
     <row r="14" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="15" t="str">
-        <f>RIGHT(C7,13)</f>
-        <v>626206E3191</v>
+        <f>RIGHT(C7,10)</f>
+        <v>26206E3191</v>
       </c>
       <c r="D14" s="17" t="str">
         <f>"*"&amp;$C$14&amp;"*"</f>
-        <v>*626206E3191*</v>
+        <v>*26206E3191*</v>
       </c>
       <c r="E14" s="3" t="str">
         <f>$D$14</f>
-        <v>*626206E3191*</v>
-      </c>
-      <c r="I14" s="10" t="s">
+        <v>*26206E3191*</v>
+      </c>
+      <c r="I14" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
     </row>
     <row r="15" spans="1:17" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="14"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="16"/>
       <c r="D15" s="18"/>
       <c r="E15" s="4" t="str">
         <f>$C$14</f>
-        <v>626206E3191</v>
+        <v>26206E3191</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -1358,15 +1358,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="25">
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="F3:H4"/>
-    <mergeCell ref="F5:O10"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
     <mergeCell ref="I14:O14"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C13:E13"/>
@@ -1383,6 +1374,15 @@
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="F3:H4"/>
+    <mergeCell ref="F5:O10"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
